--- a/data/trans_orig/P1433-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1433-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de esterilidad en 2012</t>
+          <t>Población con diagnóstico de esterilidad en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>972584</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>974643</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1325101</t>
+          <t>1324467</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1334800</t>
+          <t>1334688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2299392</t>
+          <t>2299732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2309767</t>
+          <t>2309326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>14733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1952717</t>
+          <t>1953017</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1962157</t>
+          <t>1962112</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1745457</t>
+          <t>1745899</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1753614</t>
+          <t>1753618</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3704688</t>
+          <t>3703816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3715565</t>
+          <t>3714767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -1417,97 +1417,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6995</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7161</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>6913</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>7208</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,42 +1545,42 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>455647</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>450673</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>457668</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>99,56%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>455647</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>450507</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>457668</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>931641</t>
+          <t>931936</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>11124</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18691</t>
+          <t>19322</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24342</t>
+          <t>24128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3408648</t>
+          <t>3408658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3417928</t>
+          <t>3417944</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3530257</t>
+          <t>3529626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3543576</t>
+          <t>3543762</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6944387</t>
+          <t>6944601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6959825</t>
+          <t>6959849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de esterilidad en 2016</t>
+          <t>Población con diagnóstico de esterilidad en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>749855</t>
+          <t>749863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>988999</t>
+          <t>988525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1742893</t>
+          <t>1742204</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2697,77 +2697,77 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1932</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6856</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,05%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5832</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2070902</t>
+          <t>2071796</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2805,77 +2805,77 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1987280</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1983185</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1988300</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,95%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>99,74%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1987280</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1981444</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1988300</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>4062753</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>4056903</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4064685</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>99,95%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3858</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>4062753</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>4058853</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4064685</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,95%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3055,62 +3055,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5770</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5056</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540860</t>
+          <t>540892</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>547139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>549140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1090971</t>
+          <t>1090257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3369847</t>
+          <t>3369714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3376726</t>
+          <t>3376728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3524945</t>
+          <t>3525741</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6899640</t>
+          <t>6898257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6907940</t>
+          <t>6907805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/P1433-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1433-Estudios-trans_orig.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1324467</t>
+          <t>1324841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1334688</t>
+          <t>1334812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2299732</t>
+          <t>2299307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2309326</t>
+          <t>2309338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14733</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1953017</t>
+          <t>1953021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1962112</t>
+          <t>1962123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1745899</t>
+          <t>1746298</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1753618</t>
+          <t>1753616</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3703816</t>
+          <t>3703603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3714767</t>
+          <t>3714841</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>450673</t>
+          <t>451445</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>931936</t>
+          <t>931631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>11044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>24414</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3408658</t>
+          <t>3408738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3417944</t>
+          <t>3417942</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3529626</t>
+          <t>3530017</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3543762</t>
+          <t>3543843</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6944601</t>
+          <t>6944315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6959849</t>
+          <t>6959788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>749863</t>
+          <t>748386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>988525</t>
+          <t>990047</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1742204</t>
+          <t>1741973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2071796</t>
+          <t>2072200</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1983185</t>
+          <t>1981277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4056903</t>
+          <t>4057434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540892</t>
+          <t>541512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1090257</t>
+          <t>1090158</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11461</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3369714</t>
+          <t>3369017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3376728</t>
+          <t>3376726</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3525741</t>
+          <t>3524938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6898257</t>
+          <t>6898552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6907805</t>
+          <t>6907789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
